--- a/JuvShad_2026.xlsx
+++ b/JuvShad_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Userdata\HoffmanKy\SCDNR\Compliance report\JAI-Shad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D637B71-EF36-46A8-955C-E5E4BD85F087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{AFAC5B60-E8DD-4AA9-BBE0-B3BBC87FA047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{1FBA753E-B769-4D4B-8AAC-2961CC58B177}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{1FBA753E-B769-4D4B-8AAC-2961CC58B177}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -145,7 +145,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,13 +167,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -459,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -498,13 +491,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1094,19 +1083,19 @@
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="26">
         <v>27.8</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="26">
         <v>7.67</v>
       </c>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28">
-        <v>0</v>
-      </c>
-      <c r="V2" s="28">
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26">
+        <v>0</v>
+      </c>
+      <c r="V2" s="26">
         <v>50</v>
       </c>
     </row>
@@ -1156,19 +1145,19 @@
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3" s="28">
+      <c r="P3" s="26">
         <v>28.2</v>
       </c>
-      <c r="Q3" s="28">
+      <c r="Q3" s="26">
         <v>7.69</v>
       </c>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28">
-        <v>0</v>
-      </c>
-      <c r="V3" s="28">
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26">
+        <v>0</v>
+      </c>
+      <c r="V3" s="26">
         <v>30</v>
       </c>
     </row>
@@ -1218,19 +1207,19 @@
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="26">
         <v>28.5</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="26">
         <v>7.66</v>
       </c>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28">
-        <v>0</v>
-      </c>
-      <c r="V4" s="28">
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26">
+        <v>0</v>
+      </c>
+      <c r="V4" s="26">
         <v>0</v>
       </c>
     </row>
@@ -1412,21 +1401,21 @@
       <c r="O8">
         <v>0</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="26">
         <v>28.1</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="26">
         <v>7.98</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="26">
         <v>106.9</v>
       </c>
-      <c r="S8" s="28"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="28">
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26">
         <v>0.1</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="26">
         <v>20</v>
       </c>
     </row>
@@ -1476,21 +1465,21 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="26">
         <v>28.6</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="26">
         <v>8.17</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="26">
         <v>107.7</v>
       </c>
-      <c r="S9" s="28"/>
-      <c r="T9" s="28"/>
-      <c r="U9" s="28">
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26">
         <v>0.25</v>
       </c>
-      <c r="V9" s="28">
+      <c r="V9" s="26">
         <v>20</v>
       </c>
     </row>
@@ -1540,21 +1529,21 @@
       <c r="O10">
         <v>0</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="26">
         <v>29.7</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="26">
         <v>8.51</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="26">
         <v>109.9</v>
       </c>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28">
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26">
         <v>0.5</v>
       </c>
-      <c r="V10" s="28">
+      <c r="V10" s="26">
         <v>30</v>
       </c>
     </row>
@@ -1604,21 +1593,21 @@
       <c r="O11">
         <v>0</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="26">
         <v>29.4</v>
       </c>
-      <c r="Q11" s="28">
+      <c r="Q11" s="26">
         <v>7.73</v>
       </c>
-      <c r="R11" s="28">
+      <c r="R11" s="26">
         <v>114.7</v>
       </c>
-      <c r="S11" s="28">
-        <v>0</v>
-      </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="28">
+      <c r="S11" s="26">
+        <v>0</v>
+      </c>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="26">
         <v>70</v>
       </c>
     </row>
@@ -1668,21 +1657,21 @@
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="26">
         <v>29.6</v>
       </c>
-      <c r="Q12" s="28">
+      <c r="Q12" s="26">
         <v>7.82</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="26">
         <v>114.8</v>
       </c>
-      <c r="S12" s="28">
-        <v>0</v>
-      </c>
-      <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28">
+      <c r="S12" s="26">
+        <v>0</v>
+      </c>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26">
         <v>60</v>
       </c>
     </row>
@@ -1732,21 +1721,21 @@
       <c r="O13">
         <v>0</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="26">
         <v>29.6</v>
       </c>
-      <c r="Q13" s="28">
+      <c r="Q13" s="26">
         <v>7.87</v>
       </c>
-      <c r="R13" s="28">
+      <c r="R13" s="26">
         <v>114.9</v>
       </c>
-      <c r="S13" s="28">
-        <v>0</v>
-      </c>
-      <c r="T13" s="28"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="28">
+      <c r="S13" s="26">
+        <v>0</v>
+      </c>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26">
         <v>55</v>
       </c>
     </row>
@@ -1811,7 +1800,7 @@
       <c r="U14">
         <v>0.7</v>
       </c>
-      <c r="V14" s="25">
+      <c r="V14" s="24">
         <v>0</v>
       </c>
     </row>
@@ -1876,7 +1865,7 @@
       <c r="U15">
         <v>0.8</v>
       </c>
-      <c r="V15" s="25">
+      <c r="V15" s="24">
         <v>0</v>
       </c>
     </row>
@@ -1941,7 +1930,7 @@
       <c r="U16">
         <v>0.8</v>
       </c>
-      <c r="V16" s="25">
+      <c r="V16" s="24">
         <v>0</v>
       </c>
     </row>
@@ -2006,7 +1995,7 @@
       <c r="U17">
         <v>0.9</v>
       </c>
-      <c r="V17" s="25">
+      <c r="V17" s="24">
         <v>0.6</v>
       </c>
     </row>
@@ -2071,7 +2060,7 @@
       <c r="U18">
         <v>0.7</v>
       </c>
-      <c r="V18" s="25">
+      <c r="V18" s="24">
         <v>1</v>
       </c>
     </row>
@@ -2136,20 +2125,204 @@
       <c r="U19">
         <v>0.8</v>
       </c>
-      <c r="V19" s="25">
+      <c r="V19" s="24">
         <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="23"/>
-      <c r="Q20" s="24"/>
+      <c r="A20" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1800</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>4</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>23.8</v>
+      </c>
+      <c r="Q20">
+        <v>7.72</v>
+      </c>
+      <c r="R20">
+        <v>119</v>
+      </c>
+      <c r="S20">
+        <v>0.06</v>
+      </c>
+      <c r="U20">
+        <v>1.7</v>
+      </c>
+      <c r="V20" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="23"/>
-      <c r="Q21" s="24"/>
+      <c r="A21" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>1800</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>23.9</v>
+      </c>
+      <c r="Q21">
+        <v>7.78</v>
+      </c>
+      <c r="R21">
+        <v>119</v>
+      </c>
+      <c r="S21">
+        <v>0.06</v>
+      </c>
+      <c r="U21">
+        <v>1.7</v>
+      </c>
+      <c r="V21" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
+      <c r="A22" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>1800</v>
+      </c>
+      <c r="E22">
+        <v>26</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22">
+        <v>24</v>
+      </c>
+      <c r="Q22">
+        <v>7.64</v>
+      </c>
+      <c r="R22">
+        <v>119</v>
+      </c>
+      <c r="S22">
+        <v>0.06</v>
+      </c>
+      <c r="U22">
+        <v>1.7</v>
+      </c>
+      <c r="V22" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="23"/>
@@ -2234,7 +2407,7 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="23"/>
-      <c r="V50" s="25"/>
+      <c r="V50" s="24"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="23"/>
@@ -2331,15 +2504,15 @@
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="23"/>
-      <c r="V82" s="25"/>
+      <c r="V82" s="24"/>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="23"/>
-      <c r="V83" s="25"/>
+      <c r="V83" s="24"/>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="23"/>
-      <c r="V84" s="25"/>
+      <c r="V84" s="24"/>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="23"/>
@@ -2385,19 +2558,19 @@
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="23"/>
-      <c r="V99" s="25" t="s">
+      <c r="V99" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" s="23"/>
-      <c r="V100" s="25" t="s">
+      <c r="V100" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" s="23"/>
-      <c r="V101" s="25" t="s">
+      <c r="V101" s="24" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2418,7 +2591,7 @@
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="26"/>
+    <col min="3" max="3" width="9.140625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2428,7 +2601,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -2442,121 +2615,121 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="29">
+      <c r="A2" s="27">
         <v>46237</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="28">
-        <v>1</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="28">
+      <c r="C2" s="26">
+        <v>1</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="26">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="29">
+      <c r="A3" s="27">
         <v>46237</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="28">
-        <v>2</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="28">
+      <c r="C3" s="26">
+        <v>2</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="26">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="29">
+      <c r="A4" s="27">
         <v>46266</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="28">
-        <v>1</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="28">
+      <c r="C4" s="26">
+        <v>1</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="26">
         <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="29">
+      <c r="A5" s="27">
         <v>46266</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="28">
-        <v>1</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="28">
+      <c r="C5" s="26">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="26">
         <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="29">
+      <c r="A6" s="27">
         <v>46266</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="28">
-        <v>1</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="28">
+      <c r="C6" s="26">
+        <v>1</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="26">
         <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+      <c r="A7" s="27">
         <v>46280</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="28">
-        <v>1</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="28">
+      <c r="C7" s="26">
+        <v>1</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="26">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="29">
+      <c r="A8" s="27">
         <v>46280</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="28">
-        <v>2</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="28">
+      <c r="C8" s="26">
+        <v>2</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="26">
         <v>172</v>
       </c>
     </row>
@@ -3421,177 +3594,806 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="23"/>
+      <c r="A52" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52">
+        <v>64</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="23"/>
+      <c r="A53" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53">
+        <v>67</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="23"/>
+      <c r="A54" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54">
+        <v>71</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
+      <c r="A55" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55">
+        <v>66</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="23"/>
+      <c r="A56" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56">
+        <v>67</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="23"/>
+      <c r="A57" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57">
+        <v>68</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="23"/>
+      <c r="A58" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58">
+        <v>69</v>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="23"/>
+      <c r="A59" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59">
+        <v>70</v>
+      </c>
+      <c r="F59">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="23"/>
+      <c r="A60" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60">
+        <v>71</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="23"/>
+      <c r="A61" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61">
+        <v>72</v>
+      </c>
+      <c r="F61">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="23"/>
+      <c r="A62" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62">
+        <v>73</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="23"/>
+      <c r="A63" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63">
+        <v>75</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="23"/>
-      <c r="B64" s="26"/>
-      <c r="D64" s="27"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="23"/>
-      <c r="B65" s="26"/>
-      <c r="D65" s="27"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="23"/>
-      <c r="B66" s="26"/>
-      <c r="D66" s="27"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="23"/>
-      <c r="B67" s="26"/>
-      <c r="D67" s="27"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="23"/>
-      <c r="B68" s="26"/>
-      <c r="D68" s="27"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="23"/>
-      <c r="B69" s="26"/>
-      <c r="D69" s="27"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-      <c r="B70" s="26"/>
-      <c r="D70" s="27"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-      <c r="C71"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="23"/>
-      <c r="C72"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="23"/>
-      <c r="C73"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-      <c r="C74"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-      <c r="C75"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-      <c r="C76"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-      <c r="C77"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-      <c r="C78"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-      <c r="C79"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-      <c r="C80"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="23"/>
-      <c r="C81"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="23"/>
-      <c r="C82"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="23"/>
-      <c r="C83"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="23"/>
-      <c r="C84"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="23"/>
-      <c r="C85"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="23"/>
-      <c r="C86"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="23"/>
-      <c r="C87"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="23"/>
-      <c r="C88"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="23"/>
-      <c r="C89"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="23"/>
-      <c r="C90"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64">
+        <v>100</v>
+      </c>
+      <c r="F64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65">
+        <v>56</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B66" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66">
+        <v>63</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B67" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67">
+        <v>64</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68">
+        <v>64</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69">
+        <v>65</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70">
+        <v>66</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71">
+        <v>67</v>
+      </c>
+      <c r="F71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72">
+        <v>68</v>
+      </c>
+      <c r="F72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73">
+        <v>69</v>
+      </c>
+      <c r="F73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74">
+        <v>69</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B75" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75">
+        <v>69</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76">
+        <v>69</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77">
+        <v>70</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78">
+        <v>70</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79">
+        <v>71</v>
+      </c>
+      <c r="F79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80">
+        <v>71</v>
+      </c>
+      <c r="F80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81">
+        <v>72</v>
+      </c>
+      <c r="F81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82">
+        <v>72</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83">
+        <v>72</v>
+      </c>
+      <c r="F83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84">
+        <v>73</v>
+      </c>
+      <c r="F84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85">
+        <v>73</v>
+      </c>
+      <c r="F85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B86" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86">
+        <v>74</v>
+      </c>
+      <c r="F86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87">
+        <v>74</v>
+      </c>
+      <c r="F87">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88">
+        <v>75</v>
+      </c>
+      <c r="F88">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>26</v>
+      </c>
+      <c r="E89">
+        <v>78</v>
+      </c>
+      <c r="F89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90">
+        <v>80</v>
+      </c>
+      <c r="F90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
       <c r="C91"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
       <c r="C92"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
       <c r="C93"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
       <c r="C94"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
       <c r="C95"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
       <c r="C96"/>
     </row>

--- a/JuvShad_2026.xlsx
+++ b/JuvShad_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Userdata\HoffmanKy\SCDNR\Compliance report\JAI-Shad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kyle\Desktop\SCDNR\Analyses\JAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{AFAC5B60-E8DD-4AA9-BBE0-B3BBC87FA047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB527053-6688-4787-B073-0D40956DD1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{1FBA753E-B769-4D4B-8AAC-2961CC58B177}"/>
+    <workbookView xWindow="3990" yWindow="405" windowWidth="20265" windowHeight="13755" activeTab="1" xr2:uid="{1FBA753E-B769-4D4B-8AAC-2961CC58B177}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
@@ -139,6 +139,33 @@
   </si>
   <si>
     <t>cloud cover</t>
+  </si>
+  <si>
+    <t>Santee</t>
+  </si>
+  <si>
+    <t>Congaree</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
 </sst>
 </file>
@@ -1233,6 +1260,9 @@
       <c r="C5">
         <v>1</v>
       </c>
+      <c r="D5">
+        <v>1800</v>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -1277,6 +1307,9 @@
       <c r="C6">
         <v>2</v>
       </c>
+      <c r="D6">
+        <v>1800</v>
+      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -1320,6 +1353,9 @@
       </c>
       <c r="C7">
         <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1800</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2325,81 +2361,733 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
+      <c r="A23" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23">
+        <v>900</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>5</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
+      <c r="A24" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24">
+        <v>900</v>
+      </c>
+      <c r="E24">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>12</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
+      <c r="A25" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25">
+        <v>900</v>
+      </c>
+      <c r="E25">
+        <v>26</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>15</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
+      <c r="A26" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26">
+        <v>900</v>
+      </c>
+      <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>15</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>6</v>
+      </c>
+      <c r="P26">
+        <v>22.4</v>
+      </c>
+      <c r="Q26">
+        <v>3.78</v>
+      </c>
+      <c r="R26">
+        <v>118.3</v>
+      </c>
+      <c r="S26">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
+      <c r="A27" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27">
+        <v>900</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>6</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>21.8</v>
+      </c>
+      <c r="Q27">
+        <v>3.63</v>
+      </c>
+      <c r="R27">
+        <v>84.3</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
+      <c r="A28" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28">
+        <v>900</v>
+      </c>
+      <c r="E28">
+        <v>8</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
+      <c r="A29" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29">
+        <v>900</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>26</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
+      <c r="A30" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30">
+        <v>900</v>
+      </c>
+      <c r="E30">
+        <v>7</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>67</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
+      <c r="A31" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31">
+        <v>900</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>15</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32">
+        <v>900</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>13</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>12</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>6</v>
+      </c>
+      <c r="P32">
+        <v>28.8</v>
+      </c>
+      <c r="Q32">
+        <v>4.62</v>
+      </c>
+      <c r="R32">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="S32">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33">
+        <v>900</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>41</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34">
+        <v>900</v>
+      </c>
+      <c r="E34">
+        <v>51</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>20</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35">
+        <v>900</v>
+      </c>
+      <c r="E35">
+        <v>6</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>6</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36">
+        <v>900</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>40</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="23"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="23"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">

--- a/JuvShad_2026.xlsx
+++ b/JuvShad_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kyle\Desktop\SCDNR\Analyses\JAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB527053-6688-4787-B073-0D40956DD1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A608299-DF17-4D78-AA73-94F5ED02E135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3990" yWindow="405" windowWidth="20265" windowHeight="13755" activeTab="1" xr2:uid="{1FBA753E-B769-4D4B-8AAC-2961CC58B177}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>* Did not put AMS lengths from Santee and Congaree, 2026--see physical data sheets!</t>
   </si>
 </sst>
 </file>
@@ -1066,81 +1069,66 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
-        <v>46237</v>
+        <v>46176</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="26">
-        <v>27.8</v>
-      </c>
-      <c r="Q2" s="26">
-        <v>7.67</v>
-      </c>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26">
-        <v>0</v>
-      </c>
-      <c r="V2" s="26">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
-        <v>46237</v>
+        <v>46176</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1152,13 +1140,13 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1167,39 +1155,24 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="26">
-        <v>28.2</v>
-      </c>
-      <c r="Q3" s="26">
-        <v>7.69</v>
-      </c>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26">
-        <v>0</v>
-      </c>
-      <c r="V3" s="26">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
-        <v>46237</v>
+        <v>46176</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1208,19 +1181,19 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1232,36 +1205,33 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="26">
-        <v>28.5</v>
-      </c>
-      <c r="Q4" s="26">
-        <v>7.66</v>
-      </c>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26">
-        <v>0</v>
-      </c>
-      <c r="V4" s="26">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="P4">
+        <v>23</v>
+      </c>
+      <c r="Q4">
+        <v>8.6</v>
+      </c>
+      <c r="S4">
+        <v>0.04</v>
+      </c>
+      <c r="U4">
+        <v>0.6</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
-        <v>46251</v>
+        <v>46176</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
       </c>
       <c r="D5">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1270,19 +1240,19 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1291,24 +1261,24 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
-        <v>46251</v>
+        <v>46176</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
       </c>
       <c r="D6">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1317,19 +1287,19 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1338,24 +1308,36 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="P6">
+        <v>23</v>
+      </c>
+      <c r="Q6">
+        <v>8.56</v>
+      </c>
+      <c r="S6">
+        <v>0.04</v>
+      </c>
+      <c r="U6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
-        <v>46251</v>
+        <v>46176</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1364,19 +1346,19 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1385,91 +1367,74 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
-        <v>46266</v>
+        <v>46176</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" s="26">
-        <v>28.1</v>
-      </c>
-      <c r="Q8" s="26">
-        <v>7.98</v>
-      </c>
-      <c r="R8" s="26">
-        <v>106.9</v>
-      </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="V8" s="26">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
-        <v>46266</v>
+        <v>46190</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
       </c>
       <c r="D9">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1481,62 +1446,45 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="26">
-        <v>28.6</v>
-      </c>
-      <c r="Q9" s="26">
-        <v>8.17</v>
-      </c>
-      <c r="R9" s="26">
-        <v>107.7</v>
-      </c>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26">
-        <v>0.25</v>
-      </c>
-      <c r="V9" s="26">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
-        <v>46266</v>
+        <v>46190</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
       </c>
       <c r="D10">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1545,13 +1493,13 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1560,108 +1508,86 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10" s="26">
-        <v>29.7</v>
-      </c>
-      <c r="Q10" s="26">
-        <v>8.51</v>
-      </c>
-      <c r="R10" s="26">
-        <v>109.9</v>
-      </c>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="V10" s="26">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
-        <v>46280</v>
+        <v>46190</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
       </c>
       <c r="D11">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="26">
-        <v>29.4</v>
-      </c>
-      <c r="Q11" s="26">
-        <v>7.73</v>
-      </c>
-      <c r="R11" s="26">
-        <v>114.7</v>
-      </c>
-      <c r="S11" s="26">
-        <v>0</v>
-      </c>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26">
-        <v>70</v>
+        <v>13</v>
+      </c>
+      <c r="P11">
+        <v>28.3</v>
+      </c>
+      <c r="Q11">
+        <v>6.4</v>
+      </c>
+      <c r="R11">
+        <v>147</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
-        <v>46280</v>
+        <v>46190</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
       </c>
       <c r="D12">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1673,13 +1599,13 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1691,38 +1617,21 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12" s="26">
-        <v>29.6</v>
-      </c>
-      <c r="Q12" s="26">
-        <v>7.82</v>
-      </c>
-      <c r="R12" s="26">
-        <v>114.8</v>
-      </c>
-      <c r="S12" s="26">
-        <v>0</v>
-      </c>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
-        <v>46280</v>
+        <v>46190</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
       </c>
       <c r="D13">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1731,19 +1640,19 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1755,127 +1664,104 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="26">
-        <v>29.6</v>
-      </c>
-      <c r="Q13" s="26">
-        <v>7.87</v>
-      </c>
-      <c r="R13" s="26">
-        <v>114.9</v>
-      </c>
-      <c r="S13" s="26">
-        <v>0</v>
-      </c>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="26">
-        <v>55</v>
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>26.8</v>
+      </c>
+      <c r="Q13">
+        <v>8.52</v>
+      </c>
+      <c r="R13">
+        <v>120.6</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
-        <v>46245</v>
+        <v>46190</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>6</v>
-      </c>
-      <c r="P14">
-        <v>28.6</v>
-      </c>
-      <c r="Q14">
-        <v>6.14</v>
-      </c>
-      <c r="R14">
-        <v>131.6</v>
-      </c>
-      <c r="S14">
-        <v>0.06</v>
-      </c>
-      <c r="U14">
-        <v>0.7</v>
-      </c>
-      <c r="V14" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
-        <v>46245</v>
+        <v>46190</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
       </c>
       <c r="D15">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1884,60 +1770,43 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>10</v>
-      </c>
-      <c r="P15">
-        <v>29.6</v>
-      </c>
-      <c r="Q15">
-        <v>6.14</v>
-      </c>
-      <c r="R15">
-        <v>131.6</v>
-      </c>
-      <c r="S15">
-        <v>0.06</v>
-      </c>
-      <c r="U15">
-        <v>0.8</v>
-      </c>
-      <c r="V15" s="24">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="V15" s="24"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
-        <v>46245</v>
+        <v>46204</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
       </c>
       <c r="D16">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L16">
         <v>2</v>
@@ -1949,42 +1818,24 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>2</v>
-      </c>
-      <c r="P16">
-        <v>30</v>
-      </c>
-      <c r="Q16">
-        <v>6.3</v>
-      </c>
-      <c r="R16">
-        <v>133.9</v>
-      </c>
-      <c r="S16">
-        <v>0.06</v>
-      </c>
-      <c r="U16">
-        <v>0.8</v>
-      </c>
-      <c r="V16" s="24">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
-        <v>46258</v>
+        <v>46204</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
       </c>
       <c r="D17">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1996,373 +1847,301 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>28.4</v>
+        <v>30.5</v>
       </c>
       <c r="Q17">
-        <v>6.26</v>
+        <v>5.57</v>
       </c>
       <c r="R17">
-        <v>123.2</v>
+        <v>162.69999999999999</v>
       </c>
       <c r="S17">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>0.9</v>
-      </c>
-      <c r="V17" s="24">
-        <v>0.6</v>
+        <v>0.75</v>
+      </c>
+      <c r="V17">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
-        <v>46258</v>
+        <v>46204</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
       </c>
       <c r="D18">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
-        <v>5</v>
-      </c>
-      <c r="P18">
-        <v>29.2</v>
-      </c>
-      <c r="Q18">
-        <v>6.44</v>
-      </c>
-      <c r="R18">
-        <v>122.1</v>
-      </c>
-      <c r="S18">
-        <v>0.05</v>
-      </c>
-      <c r="U18">
-        <v>0.7</v>
-      </c>
-      <c r="V18" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
-        <v>46258</v>
+        <v>46204</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
       </c>
       <c r="D19">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>2</v>
-      </c>
-      <c r="P19">
-        <v>29.6</v>
-      </c>
-      <c r="Q19">
-        <v>6.56</v>
-      </c>
-      <c r="R19">
-        <v>122.3</v>
-      </c>
-      <c r="S19">
-        <v>0.05</v>
-      </c>
-      <c r="U19">
-        <v>0.8</v>
-      </c>
-      <c r="V19" s="24">
-        <v>0.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
-        <v>46294</v>
+        <v>46204</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
       </c>
       <c r="D20">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
         <v>4</v>
       </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
       <c r="O20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>23.8</v>
+        <v>29.3</v>
       </c>
       <c r="Q20">
-        <v>7.72</v>
+        <v>6.46</v>
       </c>
       <c r="R20">
-        <v>119</v>
+        <v>119.8</v>
       </c>
       <c r="S20">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1.7</v>
-      </c>
-      <c r="V20" s="24">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="V20">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
-        <v>46294</v>
+        <v>46204</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
       </c>
       <c r="D21">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>3</v>
-      </c>
-      <c r="P21">
-        <v>23.9</v>
-      </c>
-      <c r="Q21">
-        <v>7.78</v>
-      </c>
-      <c r="R21">
-        <v>119</v>
-      </c>
-      <c r="S21">
-        <v>0.06</v>
-      </c>
-      <c r="U21">
-        <v>1.7</v>
-      </c>
-      <c r="V21" s="24">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
-        <v>46294</v>
+        <v>46204</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
       </c>
       <c r="D22">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E22">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>26</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>4</v>
-      </c>
-      <c r="H22">
-        <v>2</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>6</v>
-      </c>
-      <c r="M22">
-        <v>2</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>3</v>
-      </c>
-      <c r="P22">
-        <v>24</v>
-      </c>
-      <c r="Q22">
-        <v>7.64</v>
-      </c>
-      <c r="R22">
-        <v>119</v>
-      </c>
-      <c r="S22">
-        <v>0.06</v>
-      </c>
-      <c r="U22">
-        <v>1.7</v>
-      </c>
-      <c r="V22" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
@@ -2374,7 +2153,7 @@
         <v>900</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2386,13 +2165,13 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2401,15 +2180,15 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B24" t="s">
         <v>32</v>
@@ -2421,25 +2200,25 @@
         <v>900</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -2448,15 +2227,27 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="P24">
+        <v>29.6</v>
+      </c>
+      <c r="Q24">
+        <v>8.9</v>
+      </c>
+      <c r="R24">
+        <v>110.4</v>
+      </c>
+      <c r="S24">
+        <v>0.05</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
@@ -2468,25 +2259,25 @@
         <v>900</v>
       </c>
       <c r="E25">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2495,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2503,7 +2294,7 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
@@ -2515,25 +2306,25 @@
         <v>900</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>5</v>
+      </c>
+      <c r="J26">
         <v>6</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>4</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
       <c r="K26">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2542,27 +2333,15 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="O26">
-        <v>6</v>
-      </c>
-      <c r="P26">
-        <v>22.4</v>
-      </c>
-      <c r="Q26">
-        <v>3.78</v>
-      </c>
-      <c r="R26">
-        <v>118.3</v>
-      </c>
-      <c r="S26">
-        <v>0.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -2574,28 +2353,28 @@
         <v>900</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2604,24 +2383,12 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>21.8</v>
-      </c>
-      <c r="Q27">
-        <v>3.63</v>
-      </c>
-      <c r="R27">
-        <v>84.3</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -2633,42 +2400,54 @@
         <v>900</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="P28">
+        <v>29.1</v>
+      </c>
+      <c r="Q28">
+        <v>6.97</v>
+      </c>
+      <c r="R28">
+        <v>91</v>
+      </c>
+      <c r="S28">
+        <v>0.05</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
-        <v>46302</v>
+        <v>46219</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
@@ -2680,10 +2459,10 @@
         <v>900</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -2692,13 +2471,13 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2707,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O29">
         <v>4</v>
@@ -2715,63 +2494,78 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
-        <v>46281</v>
+        <v>46237</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>7</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="P30" s="26">
+        <v>27.8</v>
+      </c>
+      <c r="Q30" s="26">
+        <v>7.67</v>
+      </c>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26">
+        <v>0</v>
+      </c>
+      <c r="V30" s="26">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
-        <v>46281</v>
+        <v>46237</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
+        <v>29</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2786,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2804,45 +2598,60 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="P31" s="26">
+        <v>28.2</v>
+      </c>
+      <c r="Q31" s="26">
+        <v>7.69</v>
+      </c>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26">
+        <v>0</v>
+      </c>
+      <c r="V31" s="26">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
-        <v>46281</v>
+        <v>46237</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2851,57 +2660,60 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>6</v>
-      </c>
-      <c r="P32">
-        <v>28.8</v>
-      </c>
-      <c r="Q32">
-        <v>4.62</v>
-      </c>
-      <c r="R32">
-        <v>139.30000000000001</v>
-      </c>
-      <c r="S32">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="P32" s="26">
+        <v>28.5</v>
+      </c>
+      <c r="Q32" s="26">
+        <v>7.66</v>
+      </c>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26">
+        <v>0</v>
+      </c>
+      <c r="V32" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>900</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2913,39 +2725,39 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D34">
         <v>900</v>
       </c>
       <c r="E34">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2957,42 +2769,54 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>28.4</v>
+      </c>
+      <c r="Q34">
+        <v>6.2</v>
+      </c>
+      <c r="R34">
+        <v>156</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <v>900</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3001,241 +2825,2768 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O35">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
-        <v>46281</v>
+        <v>46239</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D36">
         <v>900</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
+        <v>17</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" s="23">
+        <v>46239</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37">
+        <v>900</v>
+      </c>
+      <c r="E37">
+        <v>18</v>
+      </c>
+      <c r="F37">
+        <v>8</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>8</v>
+      </c>
+      <c r="K37">
+        <v>24</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37">
+        <v>6</v>
+      </c>
+      <c r="P37">
+        <v>27.7</v>
+      </c>
+      <c r="Q37">
+        <v>6.79</v>
+      </c>
+      <c r="R37">
+        <v>113.7</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="23">
+        <v>46239</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38">
+        <v>900</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>12</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" s="23">
+        <v>46239</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" t="s">
         <v>40</v>
       </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="23"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="23"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="23"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="23"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="23"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
+      <c r="D39">
+        <v>900</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>18</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" s="23">
+        <v>46245</v>
+      </c>
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1800</v>
+      </c>
+      <c r="E40">
+        <v>5</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40">
+        <v>10</v>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>15</v>
+      </c>
+      <c r="L40">
+        <v>3</v>
+      </c>
+      <c r="M40">
+        <v>2</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>6</v>
+      </c>
+      <c r="P40">
+        <v>28.6</v>
+      </c>
+      <c r="Q40">
+        <v>6.14</v>
+      </c>
+      <c r="R40">
+        <v>131.6</v>
+      </c>
+      <c r="S40">
+        <v>0.06</v>
+      </c>
+      <c r="U40">
+        <v>0.7</v>
+      </c>
+      <c r="V40" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="23">
+        <v>46245</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>1800</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>7</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>18</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>10</v>
+      </c>
+      <c r="P41">
+        <v>29.6</v>
+      </c>
+      <c r="Q41">
+        <v>6.14</v>
+      </c>
+      <c r="R41">
+        <v>131.6</v>
+      </c>
+      <c r="S41">
+        <v>0.06</v>
+      </c>
+      <c r="U41">
+        <v>0.8</v>
+      </c>
+      <c r="V41" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="23">
+        <v>46245</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>1800</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>13</v>
+      </c>
+      <c r="I42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>12</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>2</v>
+      </c>
+      <c r="P42">
+        <v>30</v>
+      </c>
+      <c r="Q42">
+        <v>6.3</v>
+      </c>
+      <c r="R42">
+        <v>133.9</v>
+      </c>
+      <c r="S42">
+        <v>0.06</v>
+      </c>
+      <c r="U42">
+        <v>0.8</v>
+      </c>
+      <c r="V42" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="23">
+        <v>46251</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1800</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>7</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>12</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="23">
+        <v>46251</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>1800</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>9</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="23">
+        <v>46251</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45">
+        <v>1800</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>4</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46">
+        <v>900</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>5</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47">
+        <v>900</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>13</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>3</v>
+      </c>
+      <c r="P47">
+        <v>31.9</v>
+      </c>
+      <c r="Q47">
+        <v>5.2</v>
+      </c>
+      <c r="R47">
+        <v>170.7</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48">
+        <v>900</v>
+      </c>
+      <c r="E48">
+        <v>7</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>4</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
+      <c r="A49" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49">
+        <v>900</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>10</v>
+      </c>
+      <c r="L49">
+        <v>5</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>7</v>
+      </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-      <c r="V50" s="24"/>
+      <c r="A50" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50">
+        <v>900</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>4</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>2</v>
+      </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="23"/>
+      <c r="A51" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51">
+        <v>900</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>4</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>5</v>
+      </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="23"/>
+      <c r="A52" s="23">
+        <v>46253</v>
+      </c>
+      <c r="B52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52">
+        <v>900</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>8</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>2</v>
+      </c>
+      <c r="P52">
+        <v>30.4</v>
+      </c>
+      <c r="Q52">
+        <v>5.5</v>
+      </c>
+      <c r="R52">
+        <v>126</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="23"/>
+      <c r="A53" s="23">
+        <v>46258</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>1800</v>
+      </c>
+      <c r="E53">
+        <v>28</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>4</v>
+      </c>
+      <c r="L53">
+        <v>6</v>
+      </c>
+      <c r="M53">
+        <v>2</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>4</v>
+      </c>
+      <c r="P53">
+        <v>28.4</v>
+      </c>
+      <c r="Q53">
+        <v>6.26</v>
+      </c>
+      <c r="R53">
+        <v>123.2</v>
+      </c>
+      <c r="S53">
+        <v>0.05</v>
+      </c>
+      <c r="U53">
+        <v>0.9</v>
+      </c>
+      <c r="V53" s="24">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="23"/>
+      <c r="A54" s="23">
+        <v>46258</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>1800</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>7</v>
+      </c>
+      <c r="H54">
+        <v>7</v>
+      </c>
+      <c r="I54">
+        <v>9</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>10</v>
+      </c>
+      <c r="L54">
+        <v>4</v>
+      </c>
+      <c r="M54">
+        <v>4</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>5</v>
+      </c>
+      <c r="P54">
+        <v>29.2</v>
+      </c>
+      <c r="Q54">
+        <v>6.44</v>
+      </c>
+      <c r="R54">
+        <v>122.1</v>
+      </c>
+      <c r="S54">
+        <v>0.05</v>
+      </c>
+      <c r="U54">
+        <v>0.7</v>
+      </c>
+      <c r="V54" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
+      <c r="A55" s="23">
+        <v>46258</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55">
+        <v>1800</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>5</v>
+      </c>
+      <c r="H55">
+        <v>8</v>
+      </c>
+      <c r="I55">
+        <v>3</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>2</v>
+      </c>
+      <c r="P55">
+        <v>29.6</v>
+      </c>
+      <c r="Q55">
+        <v>6.56</v>
+      </c>
+      <c r="R55">
+        <v>122.3</v>
+      </c>
+      <c r="S55">
+        <v>0.05</v>
+      </c>
+      <c r="U55">
+        <v>0.8</v>
+      </c>
+      <c r="V55" s="24">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A56" s="23"/>
+      <c r="A56" s="23">
+        <v>46266</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>1800</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>3</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>2</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56" s="26">
+        <v>28.1</v>
+      </c>
+      <c r="Q56" s="26">
+        <v>7.98</v>
+      </c>
+      <c r="R56" s="26">
+        <v>106.9</v>
+      </c>
+      <c r="S56" s="26"/>
+      <c r="T56" s="26"/>
+      <c r="U56" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="V56" s="26">
+        <v>20</v>
+      </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A57" s="23"/>
+      <c r="A57" s="23">
+        <v>46266</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>1800</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>3</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>4</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57" s="26">
+        <v>28.6</v>
+      </c>
+      <c r="Q57" s="26">
+        <v>8.17</v>
+      </c>
+      <c r="R57" s="26">
+        <v>107.7</v>
+      </c>
+      <c r="S57" s="26"/>
+      <c r="T57" s="26"/>
+      <c r="U57" s="26">
+        <v>0.25</v>
+      </c>
+      <c r="V57" s="26">
+        <v>20</v>
+      </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A58" s="23"/>
+      <c r="A58" s="23">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58">
+        <v>1800</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>3</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>6</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58" s="26">
+        <v>29.7</v>
+      </c>
+      <c r="Q58" s="26">
+        <v>8.51</v>
+      </c>
+      <c r="R58" s="26">
+        <v>109.9</v>
+      </c>
+      <c r="S58" s="26"/>
+      <c r="T58" s="26"/>
+      <c r="U58" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="V58" s="26">
+        <v>30</v>
+      </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A59" s="23"/>
+      <c r="A59" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59">
+        <v>900</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>3</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A60" s="23"/>
+      <c r="A60" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60">
+        <v>900</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>3</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>11</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>4</v>
+      </c>
+      <c r="P60">
+        <v>28.6</v>
+      </c>
+      <c r="Q60">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R60">
+        <v>170.3</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A61" s="23"/>
+      <c r="A61" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61">
+        <v>900</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>7</v>
+      </c>
+      <c r="J61">
+        <v>3</v>
+      </c>
+      <c r="K61">
+        <v>51</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A62" s="23"/>
+      <c r="A62" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62">
+        <v>900</v>
+      </c>
+      <c r="E62">
+        <v>13</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>45</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>6</v>
+      </c>
+      <c r="V62" s="24"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A63" s="23"/>
+      <c r="A63" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B63" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63">
+        <v>900</v>
+      </c>
+      <c r="E63">
+        <v>10</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>12</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="V63" s="24"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A64" s="23"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="23"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="23"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="23"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="23"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="23"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="23"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="23"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A81" s="23"/>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A82" s="23"/>
-      <c r="V82" s="24"/>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A83" s="23"/>
-      <c r="V83" s="24"/>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A84" s="23"/>
-      <c r="V84" s="24"/>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A85" s="23"/>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B64" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64">
+        <v>900</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>5</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>4</v>
+      </c>
+      <c r="P64">
+        <v>28.5</v>
+      </c>
+      <c r="Q64">
+        <v>5.8</v>
+      </c>
+      <c r="R64">
+        <v>128.6</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0.3</v>
+      </c>
+      <c r="V64" s="24"/>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B65" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65">
+        <v>900</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>3</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>12</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66" s="23">
+        <v>46280</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>1800</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>3</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>21</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66" s="26">
+        <v>29.4</v>
+      </c>
+      <c r="Q66" s="26">
+        <v>7.73</v>
+      </c>
+      <c r="R66" s="26">
+        <v>114.7</v>
+      </c>
+      <c r="S66" s="26">
+        <v>0</v>
+      </c>
+      <c r="T66" s="26"/>
+      <c r="U66" s="26"/>
+      <c r="V66" s="26">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67" s="23">
+        <v>46280</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67">
+        <v>1800</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>10</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67" s="26">
+        <v>29.6</v>
+      </c>
+      <c r="Q67" s="26">
+        <v>7.82</v>
+      </c>
+      <c r="R67" s="26">
+        <v>114.8</v>
+      </c>
+      <c r="S67" s="26">
+        <v>0</v>
+      </c>
+      <c r="T67" s="26"/>
+      <c r="U67" s="26"/>
+      <c r="V67" s="26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A68" s="23">
+        <v>46280</v>
+      </c>
+      <c r="B68" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>1800</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>13</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68" s="26">
+        <v>29.6</v>
+      </c>
+      <c r="Q68" s="26">
+        <v>7.87</v>
+      </c>
+      <c r="R68" s="26">
+        <v>114.9</v>
+      </c>
+      <c r="S68" s="26">
+        <v>0</v>
+      </c>
+      <c r="T68" s="26"/>
+      <c r="U68" s="26"/>
+      <c r="V68" s="26">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A69" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69">
+        <v>900</v>
+      </c>
+      <c r="E69">
+        <v>7</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>67</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A70" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70">
+        <v>900</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>15</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A71" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71">
+        <v>900</v>
+      </c>
+      <c r="E71">
+        <v>5</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>13</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>12</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>6</v>
+      </c>
+      <c r="P71">
+        <v>28.8</v>
+      </c>
+      <c r="Q71">
+        <v>4.62</v>
+      </c>
+      <c r="R71">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="S71">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A72" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B72" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72">
+        <v>900</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>41</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A73" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73">
+        <v>900</v>
+      </c>
+      <c r="E73">
+        <v>51</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>4</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>20</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B74" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74">
+        <v>900</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>6</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" t="s">
+        <v>40</v>
+      </c>
+      <c r="D75">
+        <v>900</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>40</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>1800</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>5</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>4</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>23.8</v>
+      </c>
+      <c r="Q76">
+        <v>7.72</v>
+      </c>
+      <c r="R76">
+        <v>119</v>
+      </c>
+      <c r="S76">
+        <v>0.06</v>
+      </c>
+      <c r="U76">
+        <v>1.7</v>
+      </c>
+      <c r="V76" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>1800</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>4</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>3</v>
+      </c>
+      <c r="P77">
+        <v>23.9</v>
+      </c>
+      <c r="Q77">
+        <v>7.78</v>
+      </c>
+      <c r="R77">
+        <v>119</v>
+      </c>
+      <c r="S77">
+        <v>0.06</v>
+      </c>
+      <c r="U77">
+        <v>1.7</v>
+      </c>
+      <c r="V77" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78" s="23">
+        <v>46294</v>
+      </c>
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78">
+        <v>1800</v>
+      </c>
+      <c r="E78">
+        <v>26</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>4</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>6</v>
+      </c>
+      <c r="M78">
+        <v>2</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>3</v>
+      </c>
+      <c r="P78">
+        <v>24</v>
+      </c>
+      <c r="Q78">
+        <v>7.64</v>
+      </c>
+      <c r="R78">
+        <v>119</v>
+      </c>
+      <c r="S78">
+        <v>0.06</v>
+      </c>
+      <c r="U78">
+        <v>1.7</v>
+      </c>
+      <c r="V78" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B79" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79">
+        <v>900</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>5</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B80" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80">
+        <v>900</v>
+      </c>
+      <c r="E80">
+        <v>12</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>4</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>12</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B81" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81">
+        <v>900</v>
+      </c>
+      <c r="E81">
+        <v>26</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>10</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>15</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82">
+        <v>900</v>
+      </c>
+      <c r="E82">
+        <v>9</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>6</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>4</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>15</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>6</v>
+      </c>
+      <c r="P82">
+        <v>22.4</v>
+      </c>
+      <c r="Q82">
+        <v>3.78</v>
+      </c>
+      <c r="R82">
+        <v>118.3</v>
+      </c>
+      <c r="S82">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B83" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83">
+        <v>900</v>
+      </c>
+      <c r="E83">
+        <v>8</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>6</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>21.8</v>
+      </c>
+      <c r="Q83">
+        <v>3.63</v>
+      </c>
+      <c r="R83">
+        <v>84.3</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B84" t="s">
+        <v>33</v>
+      </c>
+      <c r="C84" t="s">
+        <v>39</v>
+      </c>
+      <c r="D84">
+        <v>900</v>
+      </c>
+      <c r="E84">
+        <v>8</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85" s="23">
+        <v>46302</v>
+      </c>
+      <c r="B85" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" t="s">
+        <v>40</v>
+      </c>
+      <c r="D85">
+        <v>900</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>26</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="23"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="23"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="23"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="23"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="23"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="23"/>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="23"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="23"/>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="23"/>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="23"/>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="23"/>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.25">
@@ -3282,7 +5633,7 @@
     <col min="3" max="3" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3301,8 +5652,11 @@
       <c r="F1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="27">
         <v>46237</v>
       </c>
@@ -3319,7 +5673,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>46237</v>
       </c>
@@ -3336,7 +5690,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="27">
         <v>46266</v>
       </c>
@@ -3353,7 +5707,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="27">
         <v>46266</v>
       </c>
@@ -3370,7 +5724,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <v>46266</v>
       </c>
@@ -3387,7 +5741,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="27">
         <v>46280</v>
       </c>
@@ -3404,7 +5758,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="27">
         <v>46280</v>
       </c>
@@ -3421,7 +5775,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>46245</v>
       </c>
@@ -3441,7 +5795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>46245</v>
       </c>
@@ -3461,7 +5815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <v>46258</v>
       </c>
@@ -3481,7 +5835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>46245</v>
       </c>
@@ -3501,7 +5855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>46258</v>
       </c>
@@ -3521,7 +5875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <v>46258</v>
       </c>
@@ -3541,7 +5895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <v>46258</v>
       </c>
@@ -3561,7 +5915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
         <v>46258</v>
       </c>
